--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -42,7 +42,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -42,7 +42,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -42,7 +42,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -7,19 +7,19 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R48-DiplomeE" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE-R47-Commissi" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_R49-DiplomeE" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE_R50-DESCGrou" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from TRE_R51-DESCGrou" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from TRE_R53-DiplomeP" r:id="rId9" sheetId="7"/>
-    <sheet name="Include from TRE_R54-DiplomeU" r:id="rId10" sheetId="8"/>
-    <sheet name="Include from TRE_R55-Certific" r:id="rId11" sheetId="9"/>
-    <sheet name="Include from TRE_R56-Attestat" r:id="rId12" sheetId="10"/>
-    <sheet name="Include from TRE_R52-Capacite" r:id="rId13" sheetId="11"/>
-    <sheet name="Include from TRE_R58-AutreTyp" r:id="rId14" sheetId="12"/>
-    <sheet name="Include from TRE_R36-AutreDip" r:id="rId15" sheetId="13"/>
-    <sheet name="Include from TRE_R226-Dip2iem" r:id="rId16" sheetId="14"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
+    <sheet name="Include #9" r:id="rId13" sheetId="11"/>
+    <sheet name="Include #10" r:id="rId14" sheetId="12"/>
+    <sheet name="Include #11" r:id="rId15" sheetId="13"/>
+    <sheet name="Include #12" r:id="rId16" sheetId="14"/>
   </sheets>
 </workbook>
 </file>
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
